--- a/out/Attention-Mamba1_repeat_4_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8927231521932764</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>3.00677127013091</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>3.60677127013091</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.60677127013091</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.2927231521932763</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.60677127013091</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001822689019570826</v>
+        <v>-0.0001847001650880557</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.2093919603791644</v>
+        <v>-0.2121850147495078</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.2927231521932763</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.60677127013091</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8927231521932764</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8927231521932764</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8927231521932764</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8927231521932764</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8927231521932764</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8927231521932764</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.2123697149145958</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.60677127013091</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.2097251852091523</v>
+        <v>-0.2125222549030874</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5428031384045294</v>
+        <v>0.5484988023194489</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.2927231521932763</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8769232935024132</v>
+        <v>0.8855290020004875</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03867460964658947</v>
+        <v>0.03908042450468911</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2927231521932763</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4105986585781835</v>
+        <v>0.4143107554255517</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06782208806406038</v>
+        <v>0.06853374905547689</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5075553184444064</v>
+        <v>0.5122849707291254</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.08239582727279603</v>
+        <v>0.08326072311740472</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.604518431618284</v>
+        <v>0.610265890222087</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02180383532703427</v>
+        <v>0.02203287345071117</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5656254077256925</v>
+        <v>0.5709646121079784</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01211421143093593</v>
+        <v>0.01224109637236306</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5680280217255905</v>
+        <v>0.5733924279724294</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02545116578525064</v>
+        <v>0.02571774274722003</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6068326339785182</v>
+        <v>0.6126046578989431</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009996045989589118</v>
+        <v>0.01010140939490448</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6013514279125058</v>
+        <v>0.6070657621800275</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.00711725717313073</v>
+        <v>0.007193154319078358</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6055862436325189</v>
+        <v>0.6113452388279389</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002799045325616153</v>
+        <v>0.002827561040791911</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6040598077281134</v>
+        <v>0.6098029632090785</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001585738388353772</v>
+        <v>0.001602693933190876</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6044321476649647</v>
+        <v>0.6101793232216454</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0006009745230317684</v>
+        <v>0.0006080207384158588</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6040467191704845</v>
+        <v>0.6097898428980186</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002790477944013724</v>
+        <v>0.0002823506757316209</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6040033356976311</v>
+        <v>0.6097460874573134</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.914496297166269e-05</v>
+        <v>9.995228826601667e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6039220455657521</v>
+        <v>0.6096642082080393</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6038740014285867</v>
+        <v>0.6096158333344476</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.026354405308807e-05</v>
+        <v>1.074052980474707e-05</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6038689776000413</v>
+        <v>0.6096108087612603</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6038651776804279</v>
+        <v>0.6096070088416469</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6038632932283834</v>
+        <v>0.6096051243896023</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6038576280713912</v>
+        <v>0.6095994592326102</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6038509733409572</v>
+        <v>0.6095928045021761</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6038454218099196</v>
+        <v>0.6095872529711386</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8927231521932764</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6038404949591448</v>
+        <v>0.6095823261203638</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6038406052046204</v>
+        <v>0.6095824363658393</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6038406787016041</v>
+        <v>0.6095825098628229</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6038408624440632</v>
+        <v>0.6095826936052822</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6038424058807197</v>
+        <v>0.6095842370419385</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6038438758203928</v>
+        <v>0.6095857069816116</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6038451252691147</v>
+        <v>0.6095869564303337</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6038464849633121</v>
+        <v>0.609588316124531</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6038442800538028</v>
+        <v>0.6095861112150217</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6038438758203928</v>
+        <v>0.6095857069816116</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6038430306050808</v>
+        <v>0.6095848617662997</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.603843581832458</v>
+        <v>0.609585412993677</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6038432510960317</v>
+        <v>0.6095850822572506</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6038429571080971</v>
+        <v>0.6095847882693161</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6038430306050808</v>
+        <v>0.6095848617662997</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6038425896231788</v>
+        <v>0.6095844207843978</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6038424793777033</v>
+        <v>0.6095843105389223</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6038424426292116</v>
+        <v>0.6095842737904306</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6038425896231788</v>
+        <v>0.6095844207843978</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6038421118927851</v>
+        <v>0.6095839430540041</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6038430673535725</v>
+        <v>0.6095848985147914</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6038430306050808</v>
+        <v>0.6095848617662997</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6038426998686544</v>
+        <v>0.6095845310298733</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6038431408505563</v>
+        <v>0.6095849720117752</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6038425161261952</v>
+        <v>0.6095843472874142</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6038423323837361</v>
+        <v>0.6095841635449549</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.603841928150326</v>
+        <v>0.609583759311545</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.603841082935014</v>
+        <v>0.609582914096233</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6038410461865223</v>
+        <v>0.6095828773477413</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6038411931804896</v>
+        <v>0.6095830243417085</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.603841119683506</v>
+        <v>0.6095829508447249</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6038411931804896</v>
+        <v>0.6095830243417085</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6038412299289815</v>
+        <v>0.6095830610902004</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.603841119683506</v>
+        <v>0.6095829508447249</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.603841560665408</v>
+        <v>0.6095833918266268</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6038414504199324</v>
+        <v>0.6095832815811513</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6038414136714404</v>
+        <v>0.6095832448326594</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6038413401744568</v>
+        <v>0.6095831713356757</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6038413034259651</v>
+        <v>0.6095831345871841</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.603841082935014</v>
+        <v>0.609582914096233</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6038410094380304</v>
+        <v>0.6095828405992494</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6038409359410468</v>
+        <v>0.6095827671022658</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6038409726895387</v>
+        <v>0.6095828038507577</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6038408624440632</v>
+        <v>0.6095826936052822</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6038409726895387</v>
+        <v>0.6095828038507577</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6038412666774732</v>
+        <v>0.6095830978386921</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_4_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.890530783292903</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>3.00677127013091</v>
+        <v>1.336187288701382</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001822689019570826</v>
+        <v>-0.0001350398863415467</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.2093919603791644</v>
+        <v>-0.1551348926054236</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.2927231521932763</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.2095742292811214</v>
+        <v>-0.1552699324917651</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.2097251852091523</v>
+        <v>-0.1553681466680007</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5428031384045294</v>
+        <v>0.3531558103870964</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8769232935024132</v>
+        <v>0.5516215461942582</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03867460964658947</v>
+        <v>0.02516227734292693</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4105986585781835</v>
+        <v>0.2482237898102486</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06782208806406038</v>
+        <v>0.04412606114034288</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5075553184444064</v>
+        <v>0.3113052375117608</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.08239582727279603</v>
+        <v>0.05360795303905098</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.604518431618284</v>
+        <v>0.3743908838313965</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02180383532703427</v>
+        <v>0.01418584251891627</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5656254077256925</v>
+        <v>0.3490865030494227</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01211421143093593</v>
+        <v>0.007879825290788473</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5680280217255905</v>
+        <v>0.35064797639863</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02545116578525064</v>
+        <v>0.01655858978799439</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6068326339785182</v>
+        <v>0.3758955265872131</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009996045989589118</v>
+        <v>0.006502098583441794</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6013514279125058</v>
+        <v>0.3723273624594249</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.00711725717313073</v>
+        <v>0.004629900708210771</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6055862436325189</v>
+        <v>0.375081142414598</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002799045325616153</v>
+        <v>0.001818647880049634</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6040598077281134</v>
+        <v>0.3740862890121899</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001585738388353772</v>
+        <v>0.001030829648230363</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6044321476649647</v>
+        <v>0.3743268790922591</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0006009745230317684</v>
+        <v>0.0003895880615090585</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6040467191704845</v>
+        <v>0.3740743975046372</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002790477944013724</v>
+        <v>0.0001799613544939169</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6040033356976311</v>
+        <v>0.3740444514738384</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.914496297166269e-05</v>
+        <v>6.281532472573384e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6039220455657521</v>
+        <v>0.3739899656126653</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.600407385783514e-05</v>
+        <v>1.503340156967809e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6038740014285867</v>
+        <v>0.3739571524778814</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.026354405308807e-05</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6038689776000413</v>
+        <v>0.3739521368403986</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>3.21904232466842e-06</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6038651776804279</v>
+        <v>0.3739479006713247</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>5.776969076452056e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6038632932283834</v>
+        <v>0.373944916792219</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6038576280713912</v>
+        <v>0.3739394730472127</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6038509733409572</v>
+        <v>0.3739334803137824</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6038454218099196</v>
+        <v>0.373928112525204</v>
       </c>
     </row>
     <row r="81">
@@ -65328,7 +65328,7 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>-4.853353791035969e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6038404949591448</v>
+        <v>0.3739281492736957</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6038406052046204</v>
+        <v>0.3739282595191712</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6038406787016041</v>
+        <v>0.3739283330161548</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6038408624440632</v>
+        <v>0.373928516758614</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6038424058807197</v>
+        <v>0.3739300601952705</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6038438758203928</v>
+        <v>0.3739315301349436</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6038451252691147</v>
+        <v>0.3739327795836656</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6038464849633121</v>
+        <v>0.3739341392778628</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6038442800538028</v>
+        <v>0.3739319343683536</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6038438758203928</v>
+        <v>0.3739315301349436</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6038430306050808</v>
+        <v>0.3739306849196316</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.603843581832458</v>
+        <v>0.3739312361470088</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6038432510960317</v>
+        <v>0.3739309054105824</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6038429571080971</v>
+        <v>0.3739306114226479</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6038430306050808</v>
+        <v>0.3739306849196316</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6038425896231788</v>
+        <v>0.3739302439377296</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6038424793777033</v>
+        <v>0.3739301336922541</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6038424426292116</v>
+        <v>0.3739300969437624</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6038425896231788</v>
+        <v>0.3739302439377296</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6038421118927851</v>
+        <v>0.373929766207336</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6038430673535725</v>
+        <v>0.3739307216681232</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6038430306050808</v>
+        <v>0.3739306849196316</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6038426998686544</v>
+        <v>0.3739303541832052</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6038431408505563</v>
+        <v>0.3739307951651071</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6038425161261952</v>
+        <v>0.373930170440746</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6038423323837361</v>
+        <v>0.3739299866982869</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.603841928150326</v>
+        <v>0.3739295824648768</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.603841082935014</v>
+        <v>0.3739287372495648</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6038410461865223</v>
+        <v>0.3739287005010731</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6038411931804896</v>
+        <v>0.3739288474950404</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.4448742778844246</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.603841119683506</v>
+        <v>0.3739287739980568</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6038411931804896</v>
+        <v>0.3739288474950404</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6038412299289815</v>
+        <v>0.3739288842435323</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.603841119683506</v>
+        <v>0.3739287739980568</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.603841560665408</v>
+        <v>0.3739292149799587</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6038414504199324</v>
+        <v>0.3739291047344832</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6038414136714404</v>
+        <v>0.3739290679859912</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6038413401744568</v>
+        <v>0.3739289944890076</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6038413034259651</v>
+        <v>0.3739289577405159</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.603841082935014</v>
+        <v>0.3739287372495648</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6038410094380304</v>
+        <v>0.3739286637525812</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6038409359410468</v>
+        <v>0.3739285902555976</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6038409726895387</v>
+        <v>0.3739286270040895</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6038408624440632</v>
+        <v>0.373928516758614</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6038409726895387</v>
+        <v>0.3739286270040895</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6038412666774732</v>
+        <v>0.373928920992024</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_4_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0005347002297639847</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.890530783292903</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>1.520104706287384e-05</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.336187288701382</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.001147812232375145</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.427500299518339</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.000534670427441597</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.536187288701382</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0007176827639341354</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.000523718073964119</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0002901684492826462</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.16</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001039037480950356</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0009272042661905289</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001342713832855225</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.001093091443181038</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001204544678330421</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.001178612932562828</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001162176951766014</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0004900898784399033</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.001378210261464119</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001503927633166313</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.001440230756998062</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.001644505187869072</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.001770611852407455</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.001880858093500137</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001775505021214485</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.001865044236183167</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.001526797190308571</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.001817008480429649</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.001767469570040703</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.001838993281126022</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.001758044585585594</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.00167703814804554</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.001407871022820473</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0002248641103506088</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.001310670748353004</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0009767636656761169</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2464387329325323</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.000830942764878273</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.2464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.001327047124505043</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.001043578609824181</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.001432308927178383</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.001380555331707001</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0007702093571424484</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0006178002804517746</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0006337519735097885</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0001447964459657669</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.536187288701382</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.001421010121703148</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.427500299518339</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.001802004873752594</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.536187288701382</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001350398863415467</v>
+        <v>-0.0001228097873588558</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1551348926054236</v>
+        <v>-0.1410848578813508</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0005148705095052719</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.536187288701382</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0004873666912317276</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0007999688386917114</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0004775281995534897</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.0008866656571626663</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.0009609237313270569</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.001031540334224701</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0006347429007291794</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0008573085069656372</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0007385965436697006</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0008496362715959549</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0008346009999513626</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.0005503557622432709</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1552699324917651</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0004926435649394989</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1553681466680007</v>
+        <v>-0.1413030785898772</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3531558103870964</v>
+        <v>0.3430759435776961</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.000672442838549614</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5516215461942582</v>
+        <v>0.5455075269401949</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02516227734292693</v>
+        <v>0.02444408894908488</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0004212167114019394</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2482237898102486</v>
+        <v>0.2507694297906451</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04412606114034288</v>
+        <v>0.04286647507980476</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.0001816246658563614</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3113052375117608</v>
+        <v>0.312050390380477</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05360795303905098</v>
+        <v>0.05207770473143044</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0008141268044710159</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3743908838313965</v>
+        <v>0.3733356134806098</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01418584251891627</v>
+        <v>0.0137812305021614</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001532765105366707</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3490865030494227</v>
+        <v>0.3487532559441898</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007879825290788473</v>
+        <v>0.007654932404912179</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.001141287386417389</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.536187288701382</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.35064797639863</v>
+        <v>0.3502700142629291</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01655858978799439</v>
+        <v>0.01608553124854583</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.001205496490001678</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.427500299518339</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3758955265872131</v>
+        <v>0.3747963065982911</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006502098583441794</v>
+        <v>0.006316804318921676</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>3.555603325366974e-05</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.536187288701382</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3723273624594249</v>
+        <v>0.3713299274241037</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004629900708210771</v>
+        <v>0.004497080702802424</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.001747142523527145</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.375081142414598</v>
+        <v>0.3740046504174054</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001818647880049634</v>
+        <v>0.001767048014493501</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.001494379714131355</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3740862890121899</v>
+        <v>0.3730381618676479</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001030829648230363</v>
+        <v>0.001000001384890174</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.001776823773980141</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3743268790922591</v>
+        <v>0.3732716264616027</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003895880615090585</v>
+        <v>0.0003778443692022413</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.001754885539412498</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3740743975046372</v>
+        <v>0.3730261429125038</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001799613544939169</v>
+        <v>0.0001744565522768361</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.001866696402430534</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3740444514738384</v>
+        <v>0.3729968658261141</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.281532472573384e-05</v>
+        <v>6.12006741370259e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.001439893618226051</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3739899656126653</v>
+        <v>0.3729435581997309</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.503340156967809e-05</v>
+        <v>1.455641581801909e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.001266691833734512</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3739571524778814</v>
+        <v>0.3729114072824419</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>4.539715033180046e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.001341195777058601</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3739521368403986</v>
+        <v>0.3729063923896011</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.001166503876447678</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3739479006713247</v>
+        <v>0.3729021562205271</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001758372411131859</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.373944916792219</v>
+        <v>0.3728991723414215</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.001533214002847672</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3739394730472127</v>
+        <v>0.3728937285964151</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.001462150365114212</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3739334803137824</v>
+        <v>0.3728877358629848</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.001418875530362129</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.373928112525204</v>
+        <v>0.3728823680744064</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.001260062679648399</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3739281492736957</v>
+        <v>0.3728824048228981</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.00131366029381752</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3739282595191712</v>
+        <v>0.3728825150683737</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001588432118296623</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3739283330161548</v>
+        <v>0.3728825885653573</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.001119408756494522</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.373928516758614</v>
+        <v>0.3728827723078164</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0009521152824163437</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3739300601952705</v>
+        <v>0.3728843157444729</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.003498977050185204</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3739315301349436</v>
+        <v>0.372885785684146</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.009621212258934975</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3739327795836656</v>
+        <v>0.372887035132868</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.02124493010342121</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3739341392778628</v>
+        <v>0.3728883948270653</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.001002399250864983</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3739319343683536</v>
+        <v>0.372886189917556</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.0001677479594945908</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2464387329325323</v>
+        <v>0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3739315301349436</v>
+        <v>0.372885785684146</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.002406660467386246</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3739306849196316</v>
+        <v>0.372884940468834</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.001389192417263985</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3739312361470088</v>
+        <v>0.3728854916962113</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.001667028293013573</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3739309054105824</v>
+        <v>0.3728851609597849</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0004039015620946884</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3739306114226479</v>
+        <v>0.3728848669718504</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-1.206807792186737e-05</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3739306849196316</v>
+        <v>0.372884940468834</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.001055294647812843</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3739302439377296</v>
+        <v>0.3728844994869321</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.001128023490309715</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3739301336922541</v>
+        <v>0.3728843892414565</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.0007786434143781662</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3739300969437624</v>
+        <v>0.3728843524929648</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.0006420332938432693</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3739302439377296</v>
+        <v>0.3728844994869321</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.002320403233170509</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.536187288701382</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.373929766207336</v>
+        <v>0.3728840217565384</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.004541346803307533</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.427500299518339</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3739307216681232</v>
+        <v>0.3728849772173257</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.0001461133360862732</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.536187288701382</v>
+        <v>-0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3739306849196316</v>
+        <v>0.372884940468834</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.001414023339748383</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3739303541832052</v>
+        <v>0.3728846097324076</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.001255376264452934</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.2464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3739307951651071</v>
+        <v>0.3728850507143096</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.0007332246750593185</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.373930170440746</v>
+        <v>0.3728844259899484</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.0003693420439958572</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3739299866982869</v>
+        <v>0.3728842422474893</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.0001136697828769684</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3739295824648768</v>
+        <v>0.3728838380140793</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.000733841210603714</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3739287372495648</v>
+        <v>0.3728829927987673</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.001080004498362541</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3739287005010731</v>
+        <v>0.3728829560502756</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.0007443036884069443</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3739288474950404</v>
+        <v>0.3728831030442428</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.001197474077343941</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.4448742778844246</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3739287739980568</v>
+        <v>0.3728830295472592</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.0008008573204278946</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3739288474950404</v>
+        <v>0.3728831030442428</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.0009973477572202682</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3739288842435323</v>
+        <v>0.3728831397927347</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.0005064979195594788</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3739287739980568</v>
+        <v>0.3728830295472592</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.001374769955873489</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.2464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3739292149799587</v>
+        <v>0.3728834705291612</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.001260599121451378</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3739291047344832</v>
+        <v>0.3728833602836856</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.00172317773103714</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3739290679859912</v>
+        <v>0.3728833235351937</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.00147143192589283</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3739289944890076</v>
+        <v>0.37288325003821</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.001528559252619743</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3739289577405159</v>
+        <v>0.3728832132897184</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.001777045428752899</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3739287372495648</v>
+        <v>0.3728829927987673</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.00141276977956295</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3739286637525812</v>
+        <v>0.3728829193017837</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.001663068309426308</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3739285902555976</v>
+        <v>0.3728828458048</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001666165888309479</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3739286270040895</v>
+        <v>0.372882882553292</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001583613455295563</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.373928516758614</v>
+        <v>0.3728827723078164</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.0006545465439558029</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.09000000000000052</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3739286270040895</v>
+        <v>0.372882882553292</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0006327293813228607</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3000000000000006</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.373928920992024</v>
+        <v>0.3728831765412264</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_4_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.0005347002297639847</v>
+        <v>-0.0005346816033124924</v>
       </c>
       <c r="JB2" t="n">
         <v>0.1199999999999999</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1.520104706287384e-05</v>
+        <v>1.521222293376923e-05</v>
       </c>
       <c r="JB3" t="n">
         <v>0.1199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.000534670427441597</v>
+        <v>0.0005346667021512985</v>
       </c>
       <c r="JB5" t="n">
         <v>0.8599999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.0007176827639341354</v>
+        <v>-0.0007176864892244339</v>
       </c>
       <c r="JB6" t="n">
         <v>0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.000523718073964119</v>
+        <v>-0.0005237217992544174</v>
       </c>
       <c r="JB7" t="n">
         <v>0.4399999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0002901684492826462</v>
+        <v>-0.0002901889383792877</v>
       </c>
       <c r="JB8" t="n">
         <v>0.16</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.001039037480950356</v>
+        <v>-0.00103902630507946</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.5799999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0009272042661905289</v>
+        <v>-0.0009272228926420212</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.8599999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.001342713832855225</v>
+        <v>-0.001342723146080971</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.001093091443181038</v>
+        <v>-0.001093072816729546</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.001204544678330421</v>
+        <v>-0.001204567030072212</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.001178612932562828</v>
+        <v>-0.00117860920727253</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.001162176951766014</v>
+        <v>-0.001162165775895119</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.8599999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.001378210261464119</v>
+        <v>-0.001378195360302925</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.001503927633166313</v>
+        <v>-0.001503946259617805</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.2599999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.001440230756998062</v>
+        <v>-0.001440223306417465</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.001644505187869072</v>
+        <v>-0.001644520089030266</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.001770611852407455</v>
+        <v>-0.001770632341504097</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.001880858093500137</v>
+        <v>-0.001880867406725883</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.001775505021214485</v>
+        <v>-0.001775497570633888</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.001865044236183167</v>
+        <v>-0.001865046098828316</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.9999999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.001526797190308571</v>
+        <v>-0.001526804640889168</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.9999999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.001817008480429649</v>
+        <v>-0.001817004755139351</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.9999999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.001767469570040703</v>
+        <v>-0.001767458394169807</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.001838993281126022</v>
+        <v>-0.001838961616158485</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.001758044585585594</v>
+        <v>-0.001758052036166191</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.00167703814804554</v>
+        <v>-0.001677019521594048</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.1199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.001407871022820473</v>
+        <v>-0.00140787661075592</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.1199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.0002248641103506088</v>
+        <v>0.0002248603850603104</v>
       </c>
       <c r="JB32" t="n">
         <v>0.1600000000000001</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.001310670748353004</v>
+        <v>-0.001310667023062706</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0009767636656761169</v>
+        <v>-0.0009767655283212662</v>
       </c>
       <c r="JB34" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.000830942764878273</v>
+        <v>-0.0008309315890073776</v>
       </c>
       <c r="JB35" t="n">
         <v>0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.001327047124505043</v>
+        <v>-0.001327035948634148</v>
       </c>
       <c r="JB36" t="n">
         <v>0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.001432308927178383</v>
+        <v>-0.001432331278920174</v>
       </c>
       <c r="JB38" t="n">
         <v>0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.001380555331707001</v>
+        <v>-0.001380538567900658</v>
       </c>
       <c r="JB39" t="n">
         <v>0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.0007702093571424484</v>
+        <v>-0.0007702410221099854</v>
       </c>
       <c r="JB40" t="n">
         <v>0.7199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0006178002804517746</v>
+        <v>-0.0006177667528390884</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.0006337519735097885</v>
+        <v>-0.0006337407976388931</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.0001447964459657669</v>
+        <v>0.0001448225229978561</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.001421010121703148</v>
+        <v>0.00142102874815464</v>
       </c>
       <c r="JB44" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.001802004873752594</v>
+        <v>0.001802040264010429</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.0004873666912317276</v>
+        <v>0.0004873517900705338</v>
       </c>
       <c r="JB47" t="n">
         <v>0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0007999688386917114</v>
+        <v>-0.0007999520748853683</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.02000000000000007</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.0004775281995534897</v>
+        <v>-0.0004775356501340866</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.16</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.0008866656571626663</v>
+        <v>-0.0008866731077432632</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.4399999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.0009609237313270569</v>
+        <v>-0.0009609442204236984</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.3</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.001031540334224701</v>
+        <v>-0.001031545922160149</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.3</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.0006347429007291794</v>
+        <v>-0.0006347540766000748</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.3</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.0008573085069656372</v>
+        <v>-0.0008573252707719803</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.3</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.0007385965436697006</v>
+        <v>-0.0007386133074760437</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.3</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0008496362715959549</v>
+        <v>-0.0008496139198541641</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.3</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.0008346009999513626</v>
+        <v>-0.0008346047252416611</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.0005503557622432709</v>
+        <v>-0.0005503259599208832</v>
       </c>
       <c r="JB58" t="n">
         <v>0.4399999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.0004926435649394989</v>
+        <v>0.0004926566034555435</v>
       </c>
       <c r="JB59" t="n">
         <v>0.4399999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.000672442838549614</v>
+        <v>-0.0006724540144205093</v>
       </c>
       <c r="JB60" t="n">
         <v>0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.0008141268044710159</v>
+        <v>-0.0008141212165355682</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.3</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.001532765105366707</v>
+        <v>-0.001532761380076408</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.1600000000000001</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.001141287386417389</v>
+        <v>0.001141328364610672</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.3</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.001205496490001678</v>
+        <v>0.001205494627356529</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.3</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>3.555603325366974e-05</v>
+        <v>3.556720912456512e-05</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.001747142523527145</v>
+        <v>-0.001747151836752892</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.5799999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.001494379714131355</v>
+        <v>-0.001494396477937698</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.8599999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.001776823773980141</v>
+        <v>-0.001776797696948051</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.001754885539412498</v>
+        <v>-0.001754863187670708</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.001439893618226051</v>
+        <v>-0.00143989734351635</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.001266691833734512</v>
+        <v>-0.001266686245799065</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.001341195777058601</v>
+        <v>-0.0013411995023489</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.001166503876447678</v>
+        <v>-0.001166494563221931</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.001758372411131859</v>
+        <v>-0.001758364960551262</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.001533214002847672</v>
+        <v>-0.001533197239041328</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.001462150365114212</v>
+        <v>-0.00146213173866272</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.001418875530362129</v>
+        <v>-0.001418910920619965</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.001260062679648399</v>
+        <v>-0.001260073855519295</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.00131366029381752</v>
+        <v>-0.001313656568527222</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.001588432118296623</v>
+        <v>-0.001588435843586922</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.1199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.001119408756494522</v>
+        <v>-0.001119388267397881</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.1199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.0009521152824163437</v>
+        <v>0.000952133908867836</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.1199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.003498977050185204</v>
+        <v>-0.003498988226056099</v>
       </c>
       <c r="JB86" t="n">
         <v>0.16</v>
@@ -70109,7 +70109,7 @@
         <v>-0.009621212258934975</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
         <v>0.372887035132868</v>
@@ -70904,7 +70904,7 @@
         <v>0.02124493010342121</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
         <v>0.3728883948270653</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.001002399250864983</v>
+        <v>-0.00100240670144558</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
         <v>0.372886189917556</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.0001677479594945908</v>
+        <v>-0.0001677367836236954</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
         <v>0.372885785684146</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.002406660467386246</v>
+        <v>-0.002406641840934753</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0.372884940468834</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.001389192417263985</v>
+        <v>-0.001389177516102791</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.001667028293013573</v>
+        <v>-0.00166703574359417</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.4399999999999999</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.0004039015620946884</v>
+        <v>-0.0004038996994495392</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0.3728848669718504</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-1.206807792186737e-05</v>
+        <v>-1.206435263156891e-05</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC95" t="n">
         <v>0.372884940468834</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.001055294647812843</v>
+        <v>-0.001055305823683739</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="JC96" t="n">
         <v>0.3728844994869321</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.001128023490309715</v>
+        <v>-0.001128027215600014</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="JC97" t="n">
         <v>0.3728843892414565</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.0007786434143781662</v>
+        <v>-0.0007786322385072708</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
         <v>0.3728843524929648</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.0006420332938432693</v>
+        <v>-0.0006420258432626724</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0.3728844994869321</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.002320403233170509</v>
+        <v>0.002320412546396255</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0.3728840217565384</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.004541346803307533</v>
+        <v>0.004541372880339622</v>
       </c>
       <c r="JB101" t="n">
         <v>0.5799999999999998</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.0001461133360862732</v>
+        <v>0.0001460947096347809</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.16</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0.372884940468834</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.001414023339748383</v>
+        <v>-0.001414021477103233</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
         <v>0.3728846097324076</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.001255376264452934</v>
+        <v>-0.001255368813872337</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0.3728850507143096</v>
@@ -84419,7 +84419,7 @@
         <v>-0.0007332246750593185</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0.3728844259899484</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.0003693420439958572</v>
+        <v>-0.0003693718463182449</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
         <v>0.3728842422474893</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.0001136697828769684</v>
+        <v>-0.0001136753708124161</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0.3728838380140793</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.000733841210603714</v>
+        <v>-0.0007338505238294601</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0.3728829927987673</v>
@@ -87599,7 +87599,7 @@
         <v>-0.001080004498362541</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0.3728829560502756</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.0007443036884069443</v>
+        <v>-0.0007443148642778397</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0.3728831030442428</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.001197474077343941</v>
+        <v>-0.001197472214698792</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0.3728830295472592</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.0008008573204278946</v>
+        <v>0.0008008480072021484</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0.3728831030442428</v>
@@ -90779,7 +90779,7 @@
         <v>-0.0009973477572202682</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0.3728831397927347</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.0005064979195594788</v>
+        <v>-0.0005064848810434341</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0.3728830295472592</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.001374769955873489</v>
+        <v>-0.001374760642647743</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0.3728834705291612</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.001260599121451378</v>
+        <v>-0.001260591670870781</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0.3728833602836856</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.00172317773103714</v>
+        <v>-0.001723174005746841</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.00147143192589283</v>
+        <v>-0.001471435651183128</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.9999999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.001528559252619743</v>
+        <v>-0.001528557389974594</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.001777045428752899</v>
+        <v>-0.001777065917849541</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.00141276977956295</v>
+        <v>-0.001412754878401756</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.001663068309426308</v>
+        <v>-0.001663075760006905</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.9999999999999998</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.001666165888309479</v>
+        <v>-0.001666175201535225</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0.372882882553292</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.001583613455295563</v>
+        <v>-0.001583628356456757</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.1199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.0006545465439558029</v>
+        <v>-0.0006545614451169968</v>
       </c>
       <c r="JB125" t="n">
         <v>0.09000000000000052</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.0006327293813228607</v>
+        <v>-0.0006327275186777115</v>
       </c>
       <c r="JB126" t="n">
         <v>0.3000000000000006</v>
